--- a/report/by_model_sampling.xlsx
+++ b/report/by_model_sampling.xlsx
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.5% ± 3.4%</t>
+          <t>53.5% ± 3.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>61.1% ± 11.0%</t>
+          <t>61.7% ± 10.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -779,11 +779,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>53.4% ± 8.0%</t>
+          <t>54.1% ± 9.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>56.6% ± 15.7%</t>
+          <t>57.3% ± 16.4%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.6% ± 11.6%</t>
+          <t>58.8% ± 11.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>69.2% ± 20.7%</t>
+          <t>66.1% ± 20.3%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>54.9% ± 9.8%</t>
+          <t>50.0% ± 0.1%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>60.2% ± 19.8%</t>
+          <t>50.3% ± 0.6%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -898,30 +898,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48.4% ± nan%</t>
+          <t>56.3% ± 13.6%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>49.9% ± nan%</t>
+          <t>65.0% ± 19.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>89.9%</t>
         </is>
       </c>
     </row>
@@ -939,30 +939,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>56.3% ± 13.6%</t>
+          <t>48.4% ± nan%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>65.0% ± 19.1%</t>
+          <t>49.9% ± nan%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>

--- a/report/by_model_sampling.xlsx
+++ b/report/by_model_sampling.xlsx
@@ -473,13 +473,13 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Commonsense Hard Set</t>
+          <t>CS Hard Set, %</t>
         </is>
       </c>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Commonsense Test Set</t>
+          <t>CS Test Set, %</t>
         </is>
       </c>
       <c r="I1" s="1" t="n"/>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>BERT-base</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -537,22 +537,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.8% ± 3.9%</t>
+          <t>52.8 ± 3.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>61.8% ± 16.7%</t>
+          <t>61.8 ± 16.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.7</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bert-base-cased</t>
+          <t>BERT-base</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -578,22 +578,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>46.0% ± 16.3%</t>
+          <t>46.0 ± 16.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>57.4% ± 7.2%</t>
+          <t>57.4 ± 7.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.0</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bert-large-cased</t>
+          <t>BERT-large</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -619,22 +619,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>53.5% ± 3.0%</t>
+          <t>53.5 ± 3.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>61.7% ± 10.1%</t>
+          <t>61.7 ± 10.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>77.7</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bert-large-cased</t>
+          <t>BERT-large</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -660,22 +660,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>54.5% ± 4.8%</t>
+          <t>54.5 ± 4.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>65.1% ± 14.8%</t>
+          <t>65.1 ± 14.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>85.4</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bert-large-cased</t>
+          <t>BERT-large</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -701,22 +701,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.4% ± 3.1%</t>
+          <t>53.4 ± 3.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>60.2% ± 12.4%</t>
+          <t>60.2 ± 12.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>74.5</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bert-large-cased</t>
+          <t>BERT-large</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -742,22 +742,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>51.6% ± nan%</t>
+          <t>51.6 ± nan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53.4% ± nan%</t>
+          <t>53.4 ± nan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.4</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>roberta-large</t>
+          <t>RoBERTa-large</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -783,22 +783,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>54.1% ± 9.0%</t>
+          <t>54.1 ± 9.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>57.3% ± 16.4%</t>
+          <t>57.3 ± 16.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.9</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>roberta-large</t>
+          <t>RoBERTa-large</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -824,22 +824,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>58.8% ± 11.2%</t>
+          <t>58.8 ± 11.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>66.1% ± 20.3%</t>
+          <t>66.1 ± 20.3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.4</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roberta-large</t>
+          <t>RoBERTa-large</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -865,22 +865,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>50.0% ± 0.1%</t>
+          <t>50.0 ± 0.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50.3% ± 0.6%</t>
+          <t>50.3 ± 0.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.0</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>microsoft/deberta-v2-xlarge</t>
+          <t>DeBERTa-v2-xlarge</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -898,30 +898,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LAST</t>
+          <t>AVG</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>56.3% ± 13.6%</t>
+          <t>48.4 ± nan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>65.0% ± 19.1%</t>
+          <t>49.9 ± nan</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>49.9</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>microsoft/deberta-v2-xlarge</t>
+          <t>DeBERTa-v2-xlarge</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -939,30 +939,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AVG</t>
+          <t>LAST</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>48.4% ± nan%</t>
+          <t>56.3 ± 13.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>49.9% ± nan%</t>
+          <t>65.0 ± 19.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>89.9</t>
         </is>
       </c>
     </row>
